--- a/planilhas/LISTA DE PROCESSO RACK SLIM SEM AÇUCAR.xlsx
+++ b/planilhas/LISTA DE PROCESSO RACK SLIM SEM AÇUCAR.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,11 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -332,16 +331,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="3" min="1" max="1"/>
-    <col width="27" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21" customWidth="1" style="3" min="3" max="3"/>
-    <col width="38.140625" customWidth="1" style="3" min="4" max="4"/>
-    <col width="8.5703125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="10.7109375" customWidth="1" style="3" min="6" max="6"/>
-    <col width="14" customWidth="1" style="3" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="38.140625" customWidth="1" min="4" max="4"/>
+    <col width="8.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -408,7 +407,7 @@
       <c r="F2" t="n">
         <v>26</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>001229</t>
         </is>
@@ -441,7 +440,7 @@
       <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>001230</t>
         </is>
@@ -474,7 +473,7 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>001231</t>
         </is>
@@ -507,7 +506,7 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>001232</t>
         </is>
@@ -540,7 +539,7 @@
       <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>001233</t>
         </is>
@@ -573,7 +572,7 @@
       <c r="F7" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>001234</t>
         </is>
@@ -606,7 +605,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>001235</t>
         </is>
@@ -639,7 +638,7 @@
       <c r="F9" t="n">
         <v>650</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>001236</t>
         </is>
@@ -672,7 +671,7 @@
       <c r="F10" t="n">
         <v>1300</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>001237</t>
         </is>
@@ -705,7 +704,7 @@
       <c r="F11" t="n">
         <v>2600</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>001238</t>
         </is>
@@ -738,7 +737,7 @@
       <c r="F12" t="n">
         <v>650</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>001239</t>
         </is>
@@ -762,7 +761,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>L 248 mm</t>
+          <t>L 198 mm</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -771,9 +770,9 @@
       <c r="F13" t="n">
         <v>650</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>001240</t>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>001258</t>
         </is>
       </c>
     </row>
@@ -804,7 +803,7 @@
       <c r="F14" t="n">
         <v>650</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>001241</t>
         </is>
@@ -837,7 +836,7 @@
       <c r="F15" t="n">
         <v>650</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>001242</t>
         </is>
@@ -870,7 +869,7 @@
       <c r="F16" t="n">
         <v>1300</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>001243</t>
         </is>
@@ -903,7 +902,7 @@
       <c r="F17" t="n">
         <v>1300</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>001244</t>
         </is>
@@ -936,7 +935,7 @@
       <c r="F18" t="n">
         <v>1300</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>001245</t>
         </is>
@@ -969,7 +968,7 @@
       <c r="F19" t="n">
         <v>325</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>001246</t>
         </is>
@@ -993,18 +992,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Estrutura Corpo</t>
+          <t>Tubo Frontal e Traseiro + Canaletas</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>325</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>001247</t>
+        <v>650</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>001259</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1025,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bandeja no Corpo</t>
+          <t>Estrutura Corpo</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1035,9 +1034,9 @@
       <c r="F21" t="n">
         <v>325</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>001248</t>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>001247</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1058,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Canaleta no Corpo</t>
+          <t>Bandeja no Corpo</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1068,9 +1067,9 @@
       <c r="F22" t="n">
         <v>325</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>001249</t>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>001248</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1091,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Canaleta na Testeira</t>
+          <t>Canaleta no Corpo</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1101,9 +1100,9 @@
       <c r="F23" t="n">
         <v>325</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>001250</t>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>001249</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1124,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Chapéu no Corpo</t>
+          <t>Canaleta na Testeira</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1134,9 +1133,9 @@
       <c r="F24" t="n">
         <v>325</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>001251</t>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>001250</t>
         </is>
       </c>
     </row>
@@ -1153,21 +1152,54 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Solda Mig</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Chapéu no Corpo</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>325</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>001251</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SOLAR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RACK SLIM SEM AÇUCAR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Solda Ponto</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Bandeja Orelha</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>4</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>1300</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>001252</t>
         </is>
